--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -738,104 +729,87 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>230</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">868
-</t>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="U4" s="3" t="n"/>
@@ -859,146 +833,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
-</t>
+          <t>565</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1016,146 +966,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>563</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1173,146 +1099,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">895
-</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>390</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">004
-</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>304</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="X7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1331,140 +1233,117 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2359
-</t>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>239</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>262</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1483,104 +1362,87 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8871
-</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4235
-</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11960
-</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92551
-</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1590,32 +1452,27 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9714
-</t>
+          <t>974</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
-</t>
+          <t>957</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1634,140 +1491,117 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
-</t>
+          <t>847</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 9
-</t>
+          <t>081 1</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1784,10 +1618,9 @@
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>284</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1797,8 +1630,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1813,62 +1645,52 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>172</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -1883,8 +1705,7 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
@@ -1904,8 +1725,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
-</t>
+          <t>589</t>
         </is>
       </c>
       <c r="Z11" s="3" t="n"/>
@@ -1924,116 +1744,97 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">431
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2571
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -2058,8 +1859,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2078,140 +1878,117 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2230,140 +2007,117 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>173</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="S14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>182</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">515
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2382,140 +2136,117 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2533,38 +2264,32 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
-</t>
+          <t>498</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2882
-</t>
+          <t>842</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2579,26 +2304,22 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9094
-</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -2608,26 +2329,22 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1382
-</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
-</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -2637,20 +2354,17 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2660,14 +2374,12 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2686,135 +2398,113 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>181</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10685
-</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810 8
-</t>
+          <t>90 21</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2832,14 +2522,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2884,8 +2572,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2900,8 +2587,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2916,8 +2602,7 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -2942,20 +2627,17 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">007
-</t>
+          <t>001</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2974,140 +2656,117 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>296</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2940
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3125,146 +2784,122 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">874
-</t>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
-</t>
+          <t>475</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3283,38 +2918,32 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -3324,98 +2953,82 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3433,128 +3046,107 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>683</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
@@ -3564,14 +3156,12 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3589,38 +3179,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3630,62 +3214,52 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
+          <t>529</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
-</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -3695,20 +3269,17 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11235
-</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9356
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
@@ -3723,8 +3294,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6528
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3743,135 +3313,113 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">054
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">841
-</t>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>281</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>247</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3889,63 +3437,53 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 4
-</t>
+          <t>19 2</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">076
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -3970,8 +3508,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3987,8 +3524,7 @@
       <c r="U25" s="3" t="n"/>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -4003,14 +3539,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4029,140 +3563,117 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
-</t>
+          <t>522</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4178,143 +3689,124 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>274</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4332,146 +3824,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">660
-</t>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">599
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4489,146 +3957,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>198</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4647,20 +4091,17 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1332
-</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">095
-</t>
+          <t>095</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4670,8 +4111,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4681,8 +4121,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4697,14 +4136,12 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
-</t>
+          <t>834</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4714,38 +4151,32 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
-</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
-</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2989
-</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>708</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4755,8 +4186,7 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
@@ -4766,8 +4196,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9162
-</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4790,141 +4219,118 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2051
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4943,8 +4349,7 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4954,14 +4359,12 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -4971,39 +4374,33 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P32" s="3" t="n"/>
@@ -5019,14 +4416,12 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>568</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -5042,14 +4437,12 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44 128
-</t>
+          <t>91 191</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -5073,140 +4466,117 @@
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="M33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>156</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2560
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">750
-</t>
+          <t>750</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5225,140 +4595,117 @@
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5374,143 +4721,124 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>209</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="W35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0188
-</t>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>188</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5529,134 +4857,112 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="R36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>218</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n"/>
@@ -5673,29 +4979,29 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88218
-</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">456
-</t>
+          <t>456</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5710,20 +5016,17 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5738,38 +5041,32 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1318
-</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10822
-</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
-</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
-</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5779,32 +5076,27 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
-</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9981
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
-</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5823,135 +5115,113 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12790 1
-</t>
-        </is>
-      </c>
-      <c r="X38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1119
-</t>
+          <t>011 1</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>208</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5969,8 +5239,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -5980,14 +5249,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -6003,38 +5270,32 @@
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -6054,14 +5315,12 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -6076,20 +5335,17 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>645</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
@@ -6113,134 +5369,112 @@
       <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
-</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">944
-</t>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="Z40" s="3" t="n"/>
@@ -6259,26 +5493,22 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">849
-</t>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -6288,110 +5518,92 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z41" s="3" t="n"/>
@@ -6409,142 +5621,119 @@
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">486
-</t>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>286</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>140</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6563,140 +5752,117 @@
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">501
-</t>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1744
-</t>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>148</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0250
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="S43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6714,146 +5880,122 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>250</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1548
-</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="R44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>218</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -6869,143 +6011,124 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11658
-</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
-</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1359
-</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
-</t>
+          <t>650</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">594
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
-</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990
-</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11911
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5179
-</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
-</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15430
-</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
-</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3929
-</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111411
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7024,140 +6147,117 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72162 8
-</t>
+          <t>28 08</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="N46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">549
-</t>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>2011 0</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="S46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
